--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120966855</v>
+        <v>120975494</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460072</v>
+        <v>460001</v>
       </c>
       <c r="R2" t="n">
-        <v>6987042</v>
+        <v>6987016</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +751,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120967414</v>
+        <v>120975472</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +797,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460141</v>
+        <v>460001</v>
       </c>
       <c r="R3" t="n">
-        <v>6987005</v>
+        <v>6987016</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,27 +857,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:26</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120967695</v>
+        <v>120967482</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,13 +927,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460093</v>
+        <v>460132</v>
       </c>
       <c r="R4" t="n">
-        <v>6987090</v>
+        <v>6987099</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1002,7 @@
         <v>120966756</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120967511</v>
+        <v>120966915</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1127,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1151,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460132</v>
+        <v>460079</v>
       </c>
       <c r="R6" t="n">
-        <v>6987099</v>
+        <v>6987037</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120975494</v>
+        <v>120967375</v>
       </c>
       <c r="B7" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,44 +1235,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460001</v>
+        <v>460141</v>
       </c>
       <c r="R7" t="n">
-        <v>6987016</v>
+        <v>6987005</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,18 +1296,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1341,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120966994</v>
+        <v>120966859</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,38 +1347,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460095</v>
+        <v>460074</v>
       </c>
       <c r="R8" t="n">
-        <v>6987027</v>
+        <v>6987042</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1416,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1426,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,10 +1456,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120970407</v>
+        <v>120967695</v>
       </c>
       <c r="B9" t="n">
-        <v>57459</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1465,25 +1468,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1493,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460112</v>
+        <v>460093</v>
       </c>
       <c r="R9" t="n">
-        <v>6987053</v>
+        <v>6987090</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1528,7 +1531,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1538,7 +1541,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120975663</v>
+        <v>120975581</v>
       </c>
       <c r="B10" t="n">
-        <v>79708</v>
+        <v>79682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,25 +1580,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1671,10 +1674,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120966915</v>
+        <v>120975663</v>
       </c>
       <c r="B11" t="n">
-        <v>90687</v>
+        <v>79711</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,41 +1686,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>460079</v>
+        <v>459885</v>
       </c>
       <c r="R11" t="n">
-        <v>6987037</v>
+        <v>6987013</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,27 +1750,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>09:51</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1783,10 +1780,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120975581</v>
+        <v>120966855</v>
       </c>
       <c r="B12" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1799,40 +1796,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>459885</v>
+        <v>460072</v>
       </c>
       <c r="R12" t="n">
-        <v>6987013</v>
+        <v>6987042</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1859,18 +1853,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1889,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120966859</v>
+        <v>120966921</v>
       </c>
       <c r="B13" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,50 +1904,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460074</v>
+        <v>460077</v>
       </c>
       <c r="R13" t="n">
-        <v>6987042</v>
+        <v>6987032</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1973,7 +1967,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1983,7 +1977,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2010,10 +2004,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120975472</v>
+        <v>120966994</v>
       </c>
       <c r="B14" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2026,40 +2020,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460001</v>
+        <v>460095</v>
       </c>
       <c r="R14" t="n">
-        <v>6987016</v>
+        <v>6987027</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2086,18 +2077,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120966921</v>
+        <v>120970407</v>
       </c>
       <c r="B15" t="n">
-        <v>79679</v>
+        <v>57462</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,25 +2128,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460077</v>
+        <v>460112</v>
       </c>
       <c r="R15" t="n">
-        <v>6987032</v>
+        <v>6987053</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2231,7 +2231,7 @@
         <v>121210353</v>
       </c>
       <c r="B16" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>121210367</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120975472</v>
+        <v>120966915</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>90697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,40 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460001</v>
+        <v>460079</v>
       </c>
       <c r="R3" t="n">
-        <v>6987016</v>
+        <v>6987037</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,18 +854,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120967482</v>
+        <v>120975472</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,37 +909,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460132</v>
+        <v>460001</v>
       </c>
       <c r="R4" t="n">
-        <v>6987099</v>
+        <v>6987016</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -960,27 +969,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120966756</v>
+        <v>120967482</v>
       </c>
       <c r="B5" t="n">
         <v>78601</v>
@@ -1035,17 +1035,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460046</v>
+        <v>460132</v>
       </c>
       <c r="R5" t="n">
-        <v>6987005</v>
+        <v>6987099</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120966915</v>
+        <v>120966756</v>
       </c>
       <c r="B6" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,34 +1127,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460079</v>
+        <v>460046</v>
       </c>
       <c r="R6" t="n">
-        <v>6987037</v>
+        <v>6987005</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120975494</v>
+        <v>120967511</v>
       </c>
       <c r="B2" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,44 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460001</v>
+        <v>460132</v>
       </c>
       <c r="R2" t="n">
-        <v>6987016</v>
+        <v>6987099</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,18 +748,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120966915</v>
+        <v>120967626</v>
       </c>
       <c r="B3" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460079</v>
+        <v>460093</v>
       </c>
       <c r="R3" t="n">
-        <v>6987037</v>
+        <v>6987090</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -866,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120975472</v>
+        <v>120966994</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,40 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460001</v>
+        <v>460095</v>
       </c>
       <c r="R4" t="n">
-        <v>6987016</v>
+        <v>6987027</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,18 +972,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120967482</v>
+        <v>120966756</v>
       </c>
       <c r="B5" t="n">
         <v>78601</v>
@@ -1035,17 +1047,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460132</v>
+        <v>460046</v>
       </c>
       <c r="R5" t="n">
-        <v>6987099</v>
+        <v>6987005</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1084,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120966756</v>
+        <v>120967375</v>
       </c>
       <c r="B6" t="n">
         <v>78601</v>
@@ -1147,11 +1159,11 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460046</v>
+        <v>460141</v>
       </c>
       <c r="R6" t="n">
         <v>6987005</v>
@@ -1186,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120967375</v>
+        <v>120966915</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1263,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460141</v>
+        <v>460079</v>
       </c>
       <c r="R7" t="n">
-        <v>6987005</v>
+        <v>6987037</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1308,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120966859</v>
+        <v>120966921</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,50 +1359,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460074</v>
+        <v>460077</v>
       </c>
       <c r="R8" t="n">
-        <v>6987042</v>
+        <v>6987032</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1419,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120967695</v>
+        <v>120970407</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>57462</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,25 +1471,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1496,13 +1499,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460093</v>
+        <v>460112</v>
       </c>
       <c r="R9" t="n">
-        <v>6987090</v>
+        <v>6987053</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1531,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1541,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1568,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120975581</v>
+        <v>120966859</v>
       </c>
       <c r="B10" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,44 +1583,50 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459885</v>
+        <v>460074</v>
       </c>
       <c r="R10" t="n">
-        <v>6987013</v>
+        <v>6987042</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1644,18 +1653,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1892,7 +1910,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120966921</v>
+        <v>120975472</v>
       </c>
       <c r="B13" t="n">
         <v>79682</v>
@@ -1926,19 +1944,22 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>460077</v>
+        <v>460001</v>
       </c>
       <c r="R13" t="n">
-        <v>6987032</v>
+        <v>6987016</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1965,27 +1986,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2004,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120966994</v>
+        <v>120975494</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2016,41 +2028,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460095</v>
+        <v>460001</v>
       </c>
       <c r="R14" t="n">
-        <v>6987027</v>
+        <v>6987016</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2077,27 +2092,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2116,10 +2122,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120970407</v>
+        <v>120975581</v>
       </c>
       <c r="B15" t="n">
-        <v>57462</v>
+        <v>79682</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2128,41 +2134,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>460112</v>
+        <v>459885</v>
       </c>
       <c r="R15" t="n">
-        <v>6987053</v>
+        <v>6987013</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2189,27 +2198,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121210353</v>
+        <v>121210367</v>
       </c>
       <c r="B16" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460189</v>
+        <v>460150</v>
       </c>
       <c r="R16" t="n">
-        <v>6987032</v>
+        <v>6987021</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121210367</v>
+        <v>121210353</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460150</v>
+        <v>460189</v>
       </c>
       <c r="R17" t="n">
-        <v>6987021</v>
+        <v>6987032</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>

--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120966859</v>
+        <v>120975663</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>79711</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,50 +1583,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>460074</v>
+        <v>459885</v>
       </c>
       <c r="R10" t="n">
-        <v>6987042</v>
+        <v>6987013</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1653,27 +1647,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:44</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1692,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120975663</v>
+        <v>120966859</v>
       </c>
       <c r="B11" t="n">
-        <v>79711</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,44 +1689,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>459885</v>
+        <v>460074</v>
       </c>
       <c r="R11" t="n">
-        <v>6987013</v>
+        <v>6987042</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1768,18 +1759,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120967511</v>
+        <v>120967482</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120967626</v>
+        <v>120967695</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120966994</v>
+        <v>120975663</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +911,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Koborgsån, Koborgsån, Jmt</t>
+          <t>Strömborgsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460095</v>
+        <v>459885</v>
       </c>
       <c r="R4" t="n">
-        <v>6987027</v>
+        <v>6987013</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,27 +975,18 @@
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120966756</v>
+        <v>120966704</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,7 +1080,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1090,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120967375</v>
+        <v>120967414</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,7 +1192,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1202,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120966915</v>
+        <v>120966921</v>
       </c>
       <c r="B7" t="n">
-        <v>90697</v>
+        <v>79685</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1245,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>460079</v>
+        <v>460077</v>
       </c>
       <c r="R7" t="n">
-        <v>6987037</v>
+        <v>6987032</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120966921</v>
+        <v>120966855</v>
       </c>
       <c r="B8" t="n">
-        <v>79682</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1381,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460077</v>
+        <v>460072</v>
       </c>
       <c r="R8" t="n">
-        <v>6987032</v>
+        <v>6987042</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1416,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1426,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1453,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120970407</v>
+        <v>120966994</v>
       </c>
       <c r="B9" t="n">
-        <v>57462</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,25 +1465,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1493,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>460112</v>
+        <v>460095</v>
       </c>
       <c r="R9" t="n">
-        <v>6987053</v>
+        <v>6987027</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1534,7 +1528,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1538,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120975663</v>
+        <v>120975472</v>
       </c>
       <c r="B10" t="n">
-        <v>79711</v>
+        <v>79685</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1577,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1614,10 +1608,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>459885</v>
+        <v>460001</v>
       </c>
       <c r="R10" t="n">
-        <v>6987013</v>
+        <v>6987016</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1680,7 +1674,7 @@
         <v>120966859</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,10 +1792,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120966855</v>
+        <v>120966915</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,21 +1808,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1838,13 +1832,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>460072</v>
+        <v>460079</v>
       </c>
       <c r="R12" t="n">
-        <v>6987042</v>
+        <v>6987037</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1873,7 +1867,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1877,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1910,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120975472</v>
+        <v>120975494</v>
       </c>
       <c r="B13" t="n">
-        <v>79682</v>
+        <v>79714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1922,25 +1916,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2016,10 +2010,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120975494</v>
+        <v>120975581</v>
       </c>
       <c r="B14" t="n">
-        <v>79711</v>
+        <v>79685</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2028,25 +2022,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2053,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>460001</v>
+        <v>459885</v>
       </c>
       <c r="R14" t="n">
-        <v>6987016</v>
+        <v>6987013</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2122,10 +2116,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120975581</v>
+        <v>120970407</v>
       </c>
       <c r="B15" t="n">
-        <v>79682</v>
+        <v>57462</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2134,44 +2128,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Strömborgsmyren, Jmt</t>
+          <t>Koborgsån, Koborgsån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>459885</v>
+        <v>460112</v>
       </c>
       <c r="R15" t="n">
-        <v>6987013</v>
+        <v>6987053</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2198,18 +2189,27 @@
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-11-06</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>121210367</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>121210353</v>
       </c>
       <c r="B17" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -2333,7 +2333,7 @@
         <v>121210353</v>
       </c>
       <c r="B17" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121210367</v>
+        <v>121210353</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460150</v>
+        <v>460189</v>
       </c>
       <c r="R16" t="n">
-        <v>6987021</v>
+        <v>6987032</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121210353</v>
+        <v>121210367</v>
       </c>
       <c r="B17" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460189</v>
+        <v>460150</v>
       </c>
       <c r="R17" t="n">
-        <v>6987032</v>
+        <v>6987021</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>

--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121210353</v>
+        <v>121210367</v>
       </c>
       <c r="B16" t="n">
-        <v>90713</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2244,21 +2244,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460189</v>
+        <v>460150</v>
       </c>
       <c r="R16" t="n">
-        <v>6987032</v>
+        <v>6987021</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121210367</v>
+        <v>121210353</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>90713</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>460150</v>
+        <v>460189</v>
       </c>
       <c r="R17" t="n">
-        <v>6987021</v>
+        <v>6987032</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>

--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -2231,7 +2231,7 @@
         <v>121210367</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>121210353</v>
       </c>
       <c r="B17" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 49016-2024 artfynd.xlsx
+++ b/artfynd/A 49016-2024 artfynd.xlsx
@@ -2231,7 +2231,7 @@
         <v>121210367</v>
       </c>
       <c r="B16" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>121210353</v>
       </c>
       <c r="B17" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
